--- a/output/pdf_financials_xlsx/PXT.xlsx
+++ b/output/pdf_financials_xlsx/PXT.xlsx
@@ -7502,40 +7502,40 @@
         <v>23.511</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>38.305</v>
+        <v>-60.931</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>44.387</v>
+        <v>-75.283</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>27.025</v>
+        <v>-33.31</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>69.88</v>
+        <v>21.702</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>35.621</v>
+        <v>-35.445</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>15.172</v>
+        <v>-88.351</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>22.767</v>
+        <v>-36.91</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>27</v>
+        <v>-33.081</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>103.394</v>
+        <v>-18.879</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>82.858</v>
+        <v>-89.55200000000001</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>54.085</v>
+        <v>-72.36</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>11.14</v>
+        <v>-98.59</v>
       </c>
     </row>
     <row r="119">
@@ -24891,7 +24891,11 @@
           <t>Exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -27900,7 +27904,11 @@
           <t>Exploration and evaluation expenditures 7</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PXT.xlsx
+++ b/output/pdf_financials_xlsx/PXT.xlsx
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.378</v>
@@ -2078,7 +2078,7 @@
         <v>-0.258</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.729</v>
+        <v>-4.788</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-12.873</v>
@@ -2139,49 +2139,49 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>1.504</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>53.772</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>181.149</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>214.093</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>218.471</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>152.399</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>115.777</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>98.738</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>103.306</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>125.899</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>121.396</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>149.351</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>194.229</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>215.77</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>200.405</v>
       </c>
     </row>
     <row r="29">
@@ -2194,52 +2194,52 @@
         <v>-0.258</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.729</v>
+        <v>-4.788</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-12.873</v>
+        <v>-11.369</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>45.866</v>
+        <v>99.63800000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>76.473</v>
+        <v>257.622</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>56.991</v>
+        <v>271.084</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-161.379</v>
+        <v>57.092</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-93.78</v>
+        <v>58.619</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-69.855</v>
+        <v>45.922</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>177.663</v>
+        <v>276.401</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>518.773</v>
+        <v>622.079</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>511.046</v>
+        <v>636.9450000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>505.423</v>
+        <v>626.819</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>812.181</v>
+        <v>961.532</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>468.294</v>
+        <v>662.523</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>313.587</v>
+        <v>529.357</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>239.175</v>
+        <v>439.58</v>
       </c>
     </row>
     <row r="30">
@@ -2254,52 +2254,52 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-33778.57142857143</v>
+        <v>-34200</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-526.2878168438267</v>
+        <v>-464.7996729354047</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>29.16923703105424</v>
+        <v>63.36642478742821</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>15.68278017488885</v>
+        <v>52.83210014273293</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>10.1923984891407</v>
+        <v>48.48127163991187</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-24.40942380818412</v>
+        <v>8.635465730094051</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-19.42757231995625</v>
+        <v>12.14357924742499</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-16.9896950343053</v>
+        <v>11.16886085985782</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>34.5494605505729</v>
+        <v>53.75067090862419</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>62.27856823867811</v>
+        <v>74.68042756918467</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>52.27803272248899</v>
+        <v>65.15701434396462</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>56.14569667373548</v>
+        <v>69.63115933254758</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>61.96572197629653</v>
+        <v>73.36052503482887</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>40.23144329896907</v>
+        <v>56.91778350515464</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>29.07322473069531</v>
+        <v>49.07765635618402</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>27.20711189980548</v>
+        <v>50.00398138984632</v>
       </c>
     </row>
     <row r="31">
@@ -2449,16 +2449,16 @@
         <v>31.95</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>56.492</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>94.82299999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>149.246</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>235.042</v>
@@ -2565,16 +2565,16 @@
         <v>31.95</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>56.492</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>94.82299999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>149.246</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>235.042</v>
@@ -3261,16 +3261,16 @@
         <v>13.753</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>70.06699999999999</v>
+        <v>13.575</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>61.451</v>
+        <v>22.451</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>108.992</v>
+        <v>14.169</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>154.582</v>
+        <v>5.336</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>4.866</v>
@@ -6449,49 +6449,49 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>1.504</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>53.772</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>181.149</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>214.093</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>218.471</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>152.399</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>115.777</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>98.738</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>103.306</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>125.899</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>121.396</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>149.351</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>194.229</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>215.77</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>200.405</v>
       </c>
     </row>
     <row r="101">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -23418,7 +23418,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -26574,7 +26574,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -48340,7 +48340,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -50377,7 +50377,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -51636,7 +51636,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -69950,7 +69950,7 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -71558,7 +71558,7 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
@@ -71760,7 +71760,7 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
@@ -73156,7 +73156,7 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">

--- a/output/pdf_financials_xlsx/PXT.xlsx
+++ b/output/pdf_financials_xlsx/PXT.xlsx
@@ -1105,43 +1105,43 @@
         <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-5.055</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-46.82</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-116.407</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-26.844</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-9.023</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-2.298</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-9.882</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-10.728</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>-24.207</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>-2.079</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>0.663</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-0</v>
+        <v>-42.279</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-0</v>
+        <v>-51.099</v>
       </c>
     </row>
     <row r="14">
@@ -2087,43 +2087,43 @@
         <v>45.866</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>76.473</v>
+        <v>81.52800000000001</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>56.991</v>
+        <v>103.811</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-161.379</v>
+        <v>-44.972</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-93.78</v>
+        <v>-66.93600000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-69.855</v>
+        <v>-60.832</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>177.663</v>
+        <v>179.961</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>518.773</v>
+        <v>528.655</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>511.046</v>
+        <v>521.774</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>505.423</v>
+        <v>529.63</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>812.181</v>
+        <v>814.26</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>468.294</v>
+        <v>467.631</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>313.587</v>
+        <v>355.866</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>239.175</v>
+        <v>290.274</v>
       </c>
     </row>
     <row r="28">
@@ -2203,43 +2203,43 @@
         <v>99.63800000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>257.622</v>
+        <v>262.677</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>271.084</v>
+        <v>317.904</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>57.092</v>
+        <v>173.499</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>58.619</v>
+        <v>85.46299999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>45.922</v>
+        <v>54.945</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>276.401</v>
+        <v>278.699</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>622.079</v>
+        <v>631.961</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>636.9450000000001</v>
+        <v>647.673</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>626.819</v>
+        <v>651.026</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>961.532</v>
+        <v>963.611</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>662.523</v>
+        <v>661.86</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>529.357</v>
+        <v>571.636</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>439.58</v>
+        <v>490.679</v>
       </c>
     </row>
     <row r="30">
@@ -2263,43 +2263,43 @@
         <v>63.36642478742821</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>52.83210014273293</v>
+        <v>53.86875953603596</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>48.48127163991187</v>
+        <v>56.85466563653533</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>8.635465730094051</v>
+        <v>26.24263764985615</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>12.14357924742499</v>
+        <v>17.70461306441054</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>11.16886085985782</v>
+        <v>13.36337833598031</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>53.75067090862419</v>
+        <v>54.19755439221513</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>74.68042756918467</v>
+        <v>75.86675918500627</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>65.15701434396462</v>
+        <v>66.25444732464906</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>69.63115933254758</v>
+        <v>72.32023141549813</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>73.36052503482887</v>
+        <v>73.51914329355289</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>56.91778350515464</v>
+        <v>56.86082474226804</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>49.07765635618402</v>
+        <v>52.99741982976253</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>50.00398138984632</v>
+        <v>55.81669681147551</v>
       </c>
     </row>
     <row r="31">
@@ -49017,7 +49017,11 @@
           <t>Net finance expense</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -50577,7 +50581,11 @@
           <t>Net finance expense $</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -53402,7 +53410,11 @@
           <t>Net finance expense $</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -56823,7 +56835,11 @@
           <t>Net finance expense $</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -58870,7 +58886,11 @@
           <t>Net finance expense $</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -63628,7 +63648,11 @@
           <t>Net finance expense $</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr"/>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E561" t="inlineStr">
         <is>
           <t>-</t>
@@ -65782,7 +65806,11 @@
           <t>Net finance expense $</t>
         </is>
       </c>
-      <c r="D583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E583" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PXT.xlsx
+++ b/output/pdf_financials_xlsx/PXT.xlsx
@@ -1331,7 +1331,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-1.036</v>
+        <v>1.114</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-28.867</v>
@@ -2315,7 +2315,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-8.291316526610643</v>
+        <v>-8.915566226490597</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>64.86674756190733</v>
@@ -4669,10 +4669,10 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>4.622</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>7.814</v>
       </c>
     </row>
     <row r="71">
@@ -4727,10 +4727,10 @@
         <v>0</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>4.622</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>7.814</v>
       </c>
     </row>
     <row r="72">
@@ -4959,10 +4959,10 @@
         <v>6</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>15.815</v>
+        <v>11.193</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>10.158</v>
+        <v>2.344</v>
       </c>
     </row>
     <row r="76">
@@ -5272,15 +5272,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q80" s="3" t="n">
+        <v>0.002523861190910823</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>0.004001161330163401</v>
       </c>
     </row>
     <row r="81">
@@ -6391,7 +6387,7 @@
         <v>-4.729</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-13.385</v>
+        <v>-13.531</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>15.635</v>
@@ -6406,7 +6402,7 @@
         <v>-86.583</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-44.621</v>
+        <v>-43.84</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-46.444</v>
@@ -6873,31 +6869,31 @@
         <v>11.023</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>12.818</v>
+        <v>25.745</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>26.86</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>16.694</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>27.684</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>27.682</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>19.128</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>30.364</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>1.462</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0</v>
+        <v>30.516</v>
       </c>
     </row>
     <row r="108">
@@ -10575,7 +10571,11 @@
           <t>Lease obligations 13</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -23711,7 +23711,11 @@
           <t>Equity settled share-based compensation expense 20</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -23810,7 +23814,11 @@
           <t>Cash settled share-based compensation expense 21</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -26752,7 +26760,11 @@
           <t>Equity settled share-based compensation expense 17</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -26849,7 +26861,11 @@
           <t>Cash settled share-based compensation expense 18</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -26946,7 +26962,11 @@
           <t>Deferred tax expense (recovery) 19</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -28977,7 +28997,11 @@
           <t>Deferred tax (recovery) 19</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -29844,7 +29868,11 @@
           <t>Equity settled share-based compensation expense 16</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -29943,7 +29971,11 @@
           <t>Cash settled share-based compensation expense 17</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -31388,7 +31420,11 @@
           <t>Equity settled share-based compensation expense 15</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -31485,7 +31521,11 @@
           <t>Cash settled share-based compensation expense 16</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -31582,7 +31622,11 @@
           <t>Deferred tax expense (recovery) 17</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -32748,7 +32792,11 @@
           <t>Deferred tax (recovery) 17</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -33419,7 +33467,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -33613,7 +33665,11 @@
           <t>Equity settled share-based compensation expense 14</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -33712,7 +33768,11 @@
           <t>Cash settled share-based compensation expense 15</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -33811,7 +33871,11 @@
           <t>Deferred tax (recovery) 16</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -34813,7 +34877,11 @@
           <t>Net (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -37464,7 +37532,11 @@
           <t>Deferred tax recovery 18</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -39052,7 +39124,11 @@
           <t>Deferred tax recovery 17</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -40555,7 +40631,11 @@
           <t>Deferred tax expense (recovery) 18</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -43272,7 +43352,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>
@@ -44278,7 +44362,11 @@
           <t>Issue of common shares – management private placement (note 9)</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -46104,7 +46192,11 @@
           <t>Issue of common shares – management private placement (note 5)</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
@@ -49387,7 +49479,11 @@
           <t>Income tax (recovery) expense total</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -72291,7 +72387,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D648" t="inlineStr"/>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E648" t="inlineStr">
         <is>
           <t>-</t>
